--- a/ACCY122/Tutorial/T03/T3.xlsx
+++ b/ACCY122/Tutorial/T03/T3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\onlym\Desktop\Manek\Notes\SIM\UOW\2025 UOW\2025 Tutorials\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseph/Desktop/SIM-UOW-Mods/ACCY122/Tutorial/T03/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3781FB4-1025-481D-BC4C-04E180C96836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{947D0BBA-8E39-E947-B63B-C061575C9C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18700" tabRatio="802" activeTab="14" xr2:uid="{98A3E0AE-1528-4E92-82CE-4DA2D69F6A7C}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="29020" windowHeight="18700" tabRatio="802" activeTab="7" xr2:uid="{98A3E0AE-1528-4E92-82CE-4DA2D69F6A7C}"/>
   </bookViews>
   <sheets>
     <sheet name="System" sheetId="4" r:id="rId1"/>
@@ -844,8 +844,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -1099,7 +1099,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1120,17 +1120,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
@@ -1143,19 +1143,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1165,11 +1165,16 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1182,11 +1187,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1233,8 +1233,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1025058" y="636227"/>
-          <a:ext cx="5375828" cy="5672912"/>
+          <a:off x="1088034" y="651971"/>
+          <a:ext cx="5942604" cy="5835598"/>
           <a:chOff x="0" y="78429"/>
           <a:chExt cx="6059328" cy="3928254"/>
         </a:xfrm>
@@ -2360,6 +2360,67 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>685800</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>520700</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8200" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7C04AE7-B640-4868-32BB-C7763200AB13}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="14820900" y="9613900"/>
+          <a:ext cx="5143500" cy="3975100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3207,7 +3268,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23B31468-06B7-4EAE-81E5-FB432EF125CF}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3217,7 +3278,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33E3D6BC-EBCC-4192-91D8-66369F108705}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3226,20 +3287,20 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47005B57-A542-46E7-A7A4-7BCE3E0049C4}">
   <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="25.1796875" customWidth="1"/>
-    <col min="3" max="3" width="12.08984375" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" customWidth="1"/>
-    <col min="6" max="7" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.1640625" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" customWidth="1"/>
+    <col min="4" max="4" width="11.5" customWidth="1"/>
+    <col min="6" max="7" width="11.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J1" s="16" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C2" s="42" t="s">
         <v>137</v>
       </c>
@@ -3259,7 +3320,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="42" t="s">
@@ -3282,7 +3343,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="38"/>
       <c r="B4" s="39" t="s">
         <v>39</v>
@@ -3303,7 +3364,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="40" t="s">
         <v>130</v>
       </c>
@@ -3330,7 +3391,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="40"/>
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
@@ -3338,7 +3399,7 @@
       <c r="E6" s="16"/>
       <c r="J6" s="16"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="40"/>
       <c r="B7" s="16"/>
       <c r="C7" s="16"/>
@@ -3348,7 +3409,7 @@
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="40">
         <v>1</v>
       </c>
@@ -3370,7 +3431,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="40"/>
       <c r="B9" s="16" t="s">
         <v>42</v>
@@ -3390,7 +3451,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="40"/>
       <c r="B10" s="16" t="s">
         <v>179</v>
@@ -3408,14 +3469,14 @@
         <v>144</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="40"/>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
       <c r="D11" s="41"/>
       <c r="E11" s="16"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="40">
         <v>2</v>
       </c>
@@ -3437,7 +3498,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B13" s="16" t="s">
         <v>189</v>
       </c>
@@ -3456,7 +3517,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="8"/>
       <c r="D14" s="9"/>
       <c r="F14" s="16" t="s">
@@ -3469,11 +3530,11 @@
         <v>144</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="8"/>
       <c r="D15" s="9"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="8">
         <v>3</v>
       </c>
@@ -3494,7 +3555,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="8"/>
       <c r="B17" t="s">
         <v>198</v>
@@ -3512,7 +3573,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="8"/>
       <c r="B18" t="s">
         <v>199</v>
@@ -3528,11 +3589,11 @@
         <v>144</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="8"/>
       <c r="D19" s="9"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="8">
         <v>4</v>
       </c>
@@ -3553,7 +3614,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
       <c r="B21" t="s">
         <v>204</v>
@@ -3571,7 +3632,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="14" t="s">
         <v>202</v>
@@ -3588,7 +3649,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>5</v>
       </c>
@@ -3608,7 +3669,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>210</v>
       </c>
@@ -3625,7 +3686,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
         <v>208</v>
       </c>
@@ -3648,20 +3709,20 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB229621-CCAD-4D6B-8775-173717B4D4BE}">
   <dimension ref="A1:K32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.81640625" customWidth="1"/>
-    <col min="7" max="7" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.26953125" customWidth="1"/>
-    <col min="9" max="9" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.08984375" customWidth="1"/>
+    <col min="2" max="2" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>211</v>
       </c>
@@ -3684,7 +3745,7 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -3705,7 +3766,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -3738,7 +3799,7 @@
       </c>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
@@ -3767,7 +3828,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -3792,7 +3853,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -3809,7 +3870,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="17"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -3825,7 +3886,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -3850,7 +3911,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2</v>
       </c>
@@ -3873,7 +3934,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>3</v>
       </c>
@@ -3898,7 +3959,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>4</v>
       </c>
@@ -3923,7 +3984,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>5</v>
       </c>
@@ -3946,7 +4007,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -3959,7 +4020,7 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -3972,7 +4033,7 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
     </row>
-    <row r="15" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -3985,7 +4046,7 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
-    <row r="16" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -3998,7 +4059,7 @@
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
-    <row r="17" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -4011,7 +4072,7 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
     </row>
-    <row r="18" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -4024,7 +4085,7 @@
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
     </row>
-    <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -4037,7 +4098,7 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -4050,7 +4111,7 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -4063,7 +4124,7 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
     </row>
-    <row r="22" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -4076,7 +4137,7 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
     </row>
-    <row r="23" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -4089,7 +4150,7 @@
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
     </row>
-    <row r="24" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -4102,7 +4163,7 @@
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
     </row>
-    <row r="25" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -4115,7 +4176,7 @@
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
     </row>
-    <row r="26" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -4128,7 +4189,7 @@
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
     </row>
-    <row r="27" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -4141,7 +4202,7 @@
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
     </row>
-    <row r="28" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -4154,7 +4215,7 @@
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
     </row>
-    <row r="29" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -4167,7 +4228,7 @@
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
     </row>
-    <row r="30" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -4180,7 +4241,7 @@
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
     </row>
-    <row r="31" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -4193,7 +4254,7 @@
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
     </row>
-    <row r="32" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -4215,26 +4276,26 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34AA0D00-A6CD-4347-9B5A-2377B0DEA2E4}">
   <dimension ref="A1:N24"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.81640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.81640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.7265625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.08984375" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.7265625" style="1"/>
+    <col min="1" max="1" width="8.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.83203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.83203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.1640625" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>129</v>
       </c>
@@ -4251,7 +4312,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -4265,7 +4326,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -4306,7 +4367,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D5" s="1" t="s">
         <v>124</v>
       </c>
@@ -4338,7 +4399,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -4353,7 +4414,7 @@
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="18"/>
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
@@ -4375,7 +4436,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="18"/>
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
@@ -4392,7 +4453,7 @@
       </c>
       <c r="M8" s="18"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="18"/>
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
@@ -4410,7 +4471,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="18"/>
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
@@ -4430,7 +4491,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="18"/>
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
@@ -4450,7 +4511,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="18"/>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -4470,7 +4531,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>10</v>
       </c>
@@ -4505,7 +4566,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="18"/>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
@@ -4522,7 +4583,7 @@
       <c r="L14" s="18"/>
       <c r="M14" s="18"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
@@ -4537,12 +4598,12 @@
       <c r="L15" s="18"/>
       <c r="M15" s="18"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="18">
         <v>1</v>
       </c>
       <c r="B16" s="18"/>
-      <c r="C16" s="56">
+      <c r="C16" s="52">
         <v>1500</v>
       </c>
       <c r="D16" s="18"/>
@@ -4553,14 +4614,14 @@
       <c r="J16" s="18"/>
       <c r="K16" s="18"/>
       <c r="L16" s="18"/>
-      <c r="M16" s="57">
+      <c r="M16" s="53">
         <v>1500</v>
       </c>
       <c r="N16" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="18">
         <v>2</v>
       </c>
@@ -4569,21 +4630,21 @@
       <c r="D17" s="18"/>
       <c r="E17" s="18"/>
       <c r="F17" s="18"/>
-      <c r="G17" s="57">
+      <c r="G17" s="53">
         <v>-14500</v>
       </c>
       <c r="I17" s="18"/>
       <c r="J17" s="18"/>
       <c r="K17" s="18"/>
       <c r="L17" s="18"/>
-      <c r="M17" s="56">
+      <c r="M17" s="52">
         <v>-14500</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="18">
         <v>3</v>
       </c>
@@ -4593,20 +4654,20 @@
       <c r="E18" s="18"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
-      <c r="I18" s="57">
+      <c r="I18" s="53">
         <v>5600</v>
       </c>
       <c r="J18" s="18"/>
       <c r="K18" s="18"/>
       <c r="L18" s="18"/>
-      <c r="M18" s="56">
+      <c r="M18" s="52">
         <v>-5600</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="18">
         <v>4</v>
       </c>
@@ -4617,19 +4678,19 @@
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
       <c r="I19" s="18"/>
-      <c r="J19" s="56">
+      <c r="J19" s="52">
         <v>-990</v>
       </c>
       <c r="K19" s="18"/>
       <c r="L19" s="18"/>
-      <c r="M19" s="57">
+      <c r="M19" s="53">
         <v>990</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="18"/>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
@@ -4646,7 +4707,7 @@
       <c r="L20" s="18"/>
       <c r="M20" s="18"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="18"/>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
@@ -4663,7 +4724,7 @@
       <c r="L21" s="18"/>
       <c r="M21" s="18"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
         <v>10</v>
       </c>
@@ -4718,7 +4779,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="18"/>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
@@ -4733,7 +4794,7 @@
       <c r="L23" s="18"/>
       <c r="M23" s="18"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G24" s="47">
         <f>SUM(B22:G22)</f>
         <v>130600</v>
@@ -4756,22 +4817,22 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{966A4206-75B3-4DD9-B080-59DADF2AC8E6}">
   <dimension ref="A1:Q26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.81640625" customWidth="1"/>
-    <col min="3" max="3" width="11.7265625" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="6.08984375" hidden="1" customWidth="1"/>
-    <col min="6" max="7" width="8.81640625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="31.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.83203125" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="6.1640625" hidden="1" customWidth="1"/>
+    <col min="6" max="7" width="8.83203125" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="0" hidden="1" customWidth="1"/>
-    <col min="9" max="10" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="8.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>156</v>
       </c>
@@ -4808,7 +4869,7 @@
       <c r="P1" s="21"/>
       <c r="Q1" s="1"/>
     </row>
-    <row r="2" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>220</v>
@@ -4841,7 +4902,7 @@
       </c>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>72</v>
       </c>
@@ -4882,7 +4943,7 @@
       </c>
       <c r="Q3" s="1"/>
     </row>
-    <row r="4" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>75</v>
       </c>
@@ -4912,7 +4973,7 @@
       <c r="P4" s="24"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>76</v>
       </c>
@@ -4942,7 +5003,7 @@
       <c r="P5" s="24"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>96</v>
       </c>
@@ -4976,7 +5037,7 @@
       <c r="P6" s="24"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -5006,7 +5067,7 @@
       <c r="P7" s="24"/>
       <c r="Q7" s="1"/>
     </row>
-    <row r="8" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>146</v>
       </c>
@@ -5040,7 +5101,7 @@
       </c>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>83</v>
       </c>
@@ -5070,7 +5131,7 @@
       </c>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>154</v>
       </c>
@@ -5100,7 +5161,7 @@
       </c>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>155</v>
       </c>
@@ -5130,7 +5191,7 @@
       <c r="P11" s="24"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>147</v>
       </c>
@@ -5160,7 +5221,7 @@
       <c r="P12" s="24"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>148</v>
       </c>
@@ -5194,7 +5255,7 @@
       <c r="P13" s="24"/>
       <c r="Q13" s="1"/>
     </row>
-    <row r="14" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>91</v>
       </c>
@@ -5224,7 +5285,7 @@
       <c r="P14" s="24"/>
       <c r="Q14" s="1"/>
     </row>
-    <row r="15" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>149</v>
       </c>
@@ -5254,7 +5315,7 @@
       <c r="P15" s="24"/>
       <c r="Q15" s="1"/>
     </row>
-    <row r="16" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>150</v>
       </c>
@@ -5286,7 +5347,7 @@
       </c>
       <c r="Q16" s="1"/>
     </row>
-    <row r="17" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>151</v>
       </c>
@@ -5318,7 +5379,7 @@
       <c r="P17" s="24"/>
       <c r="Q17" s="1"/>
     </row>
-    <row r="18" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>152</v>
       </c>
@@ -5350,7 +5411,7 @@
       <c r="P18" s="24"/>
       <c r="Q18" s="1"/>
     </row>
-    <row r="19" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="23"/>
@@ -5369,7 +5430,7 @@
       <c r="P19" s="24"/>
       <c r="Q19" s="1"/>
     </row>
-    <row r="20" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>153</v>
       </c>
@@ -5395,7 +5456,7 @@
       </c>
       <c r="Q20" s="50"/>
     </row>
-    <row r="21" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="23"/>
@@ -5414,7 +5475,7 @@
       <c r="P21" s="24"/>
       <c r="Q21" s="1"/>
     </row>
-    <row r="22" spans="1:17" ht="17.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>68</v>
       </c>
@@ -5465,7 +5526,7 @@
       </c>
       <c r="Q22" s="1"/>
     </row>
-    <row r="23" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -5484,7 +5545,7 @@
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
     </row>
-    <row r="24" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -5503,7 +5564,7 @@
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
     </row>
-    <row r="25" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -5522,7 +5583,7 @@
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
     </row>
-    <row r="26" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -5550,28 +5611,28 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4F9196-7C44-469D-BD80-0EF82F01F5AC}">
   <dimension ref="A1:Q26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.81640625" customWidth="1"/>
-    <col min="3" max="3" width="11.7265625" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="6.08984375" hidden="1" customWidth="1"/>
-    <col min="6" max="7" width="8.81640625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="4.81640625" hidden="1" customWidth="1"/>
-    <col min="9" max="10" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.453125" customWidth="1"/>
-    <col min="12" max="12" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.83203125" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="6.1640625" hidden="1" customWidth="1"/>
+    <col min="6" max="7" width="8.83203125" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="4.83203125" hidden="1" customWidth="1"/>
+    <col min="9" max="10" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.5" customWidth="1"/>
+    <col min="12" max="12" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="8.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>156</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="58" t="s">
+      <c r="C1" s="54" t="s">
         <v>51</v>
       </c>
       <c r="D1" s="21"/>
@@ -5603,7 +5664,7 @@
       <c r="P1" s="21"/>
       <c r="Q1" s="1"/>
     </row>
-    <row r="2" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>220</v>
@@ -5636,7 +5697,7 @@
       </c>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>72</v>
       </c>
@@ -5677,7 +5738,7 @@
       </c>
       <c r="Q3" s="1"/>
     </row>
-    <row r="4" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>75</v>
       </c>
@@ -5707,7 +5768,7 @@
       <c r="P4" s="24"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>76</v>
       </c>
@@ -5737,7 +5798,7 @@
       <c r="P5" s="24"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>96</v>
       </c>
@@ -5771,7 +5832,7 @@
       <c r="P6" s="24"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -5801,7 +5862,7 @@
       <c r="P7" s="24"/>
       <c r="Q7" s="1"/>
     </row>
-    <row r="8" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>146</v>
       </c>
@@ -5835,7 +5896,7 @@
       </c>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>83</v>
       </c>
@@ -5865,7 +5926,7 @@
       </c>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>154</v>
       </c>
@@ -5897,7 +5958,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>155</v>
       </c>
@@ -5925,7 +5986,7 @@
       <c r="P11" s="24"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>147</v>
       </c>
@@ -5955,7 +6016,7 @@
       <c r="P12" s="24"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>148</v>
       </c>
@@ -5989,7 +6050,7 @@
       <c r="P13" s="24"/>
       <c r="Q13" s="1"/>
     </row>
-    <row r="14" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>91</v>
       </c>
@@ -6019,7 +6080,7 @@
       <c r="P14" s="24"/>
       <c r="Q14" s="1"/>
     </row>
-    <row r="15" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>149</v>
       </c>
@@ -6049,7 +6110,7 @@
       <c r="P15" s="24"/>
       <c r="Q15" s="1"/>
     </row>
-    <row r="16" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>150</v>
       </c>
@@ -6082,7 +6143,7 @@
       </c>
       <c r="Q16" s="1"/>
     </row>
-    <row r="17" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>151</v>
       </c>
@@ -6114,7 +6175,7 @@
       <c r="P17" s="24"/>
       <c r="Q17" s="1"/>
     </row>
-    <row r="18" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>152</v>
       </c>
@@ -6146,7 +6207,7 @@
       <c r="P18" s="24"/>
       <c r="Q18" s="1"/>
     </row>
-    <row r="19" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="23"/>
@@ -6165,7 +6226,7 @@
       <c r="P19" s="24"/>
       <c r="Q19" s="1"/>
     </row>
-    <row r="20" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>153</v>
       </c>
@@ -6188,7 +6249,7 @@
       <c r="P20" s="49"/>
       <c r="Q20" s="50"/>
     </row>
-    <row r="21" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="23"/>
@@ -6207,7 +6268,7 @@
       <c r="P21" s="24"/>
       <c r="Q21" s="1"/>
     </row>
-    <row r="22" spans="1:17" ht="17.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>68</v>
       </c>
@@ -6258,7 +6319,7 @@
       </c>
       <c r="Q22" s="1"/>
     </row>
-    <row r="23" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -6277,7 +6338,7 @@
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
     </row>
-    <row r="24" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -6296,7 +6357,7 @@
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
     </row>
-    <row r="25" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -6315,7 +6376,7 @@
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
     </row>
-    <row r="26" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -6343,20 +6404,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6630C2FA-7F47-4646-A4FB-C656FFCA9DC7}">
   <dimension ref="B1:X20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.453125" customWidth="1"/>
-    <col min="7" max="7" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="2.08984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="37.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.6328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.54296875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.26953125" customWidth="1"/>
-    <col min="21" max="21" width="6.08984375" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="37.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.33203125" customWidth="1"/>
+    <col min="21" max="21" width="6.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:24" x14ac:dyDescent="0.2">
       <c r="G1" t="s">
         <v>24</v>
       </c>
@@ -6379,7 +6440,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="2" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B2" s="4" t="s">
         <v>25</v>
       </c>
@@ -6404,7 +6465,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="3" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:24" x14ac:dyDescent="0.2">
       <c r="F3" t="s">
         <v>26</v>
       </c>
@@ -6443,7 +6504,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="4" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C4" s="4" t="s">
         <v>30</v>
       </c>
@@ -6475,7 +6536,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="5" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="5" t="s">
@@ -6497,12 +6558,12 @@
       <c r="W5" s="16"/>
       <c r="X5" s="16"/>
     </row>
-    <row r="6" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="C6" s="52" t="s">
+    <row r="6" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="C6" s="57" t="s">
         <v>38</v>
       </c>
       <c r="D6" s="4"/>
-      <c r="E6" s="60" t="s">
+      <c r="E6" s="56" t="s">
         <v>39</v>
       </c>
       <c r="F6" t="s">
@@ -6535,8 +6596,8 @@
       <c r="W6" s="16"/>
       <c r="X6" s="16"/>
     </row>
-    <row r="7" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="C7" s="52"/>
+    <row r="7" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="C7" s="57"/>
       <c r="D7" s="4"/>
       <c r="E7" s="5" t="s">
         <v>35</v>
@@ -6556,10 +6617,10 @@
       <c r="W7" s="16"/>
       <c r="X7" s="16"/>
     </row>
-    <row r="8" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="C8" s="52"/>
+    <row r="8" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="C8" s="57"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="60" t="s">
+      <c r="E8" s="56" t="s">
         <v>45</v>
       </c>
       <c r="F8" t="s">
@@ -6578,8 +6639,8 @@
       <c r="W8" s="16"/>
       <c r="X8" s="16"/>
     </row>
-    <row r="9" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="C9" s="52"/>
+    <row r="9" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="C9" s="57"/>
       <c r="D9" s="4"/>
       <c r="E9" s="5" t="s">
         <v>35</v>
@@ -6595,10 +6656,10 @@
       <c r="W9" s="16"/>
       <c r="X9" s="16"/>
     </row>
-    <row r="10" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="C10" s="52"/>
+    <row r="10" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="C10" s="57"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="60" t="s">
+      <c r="E10" s="56" t="s">
         <v>47</v>
       </c>
       <c r="F10" t="s">
@@ -6632,11 +6693,11 @@
       <c r="W10" s="16"/>
       <c r="X10" s="16"/>
     </row>
-    <row r="11" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="59" t="s">
+      <c r="F11" s="55" t="s">
         <v>51</v>
       </c>
       <c r="G11" s="10" t="s">
@@ -6662,7 +6723,7 @@
       <c r="W11" s="16"/>
       <c r="X11" s="16"/>
     </row>
-    <row r="12" spans="2:24" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:24" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="5" t="s">
@@ -6679,7 +6740,7 @@
       </c>
       <c r="O12" s="9"/>
     </row>
-    <row r="13" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C13" s="4" t="s">
         <v>57</v>
       </c>
@@ -6696,7 +6757,7 @@
       <c r="M13" s="8"/>
       <c r="O13" s="9"/>
     </row>
-    <row r="14" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:24" x14ac:dyDescent="0.2">
       <c r="F14" t="s">
         <v>60</v>
       </c>
@@ -6714,7 +6775,7 @@
       </c>
       <c r="O14" s="9"/>
     </row>
-    <row r="15" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:24" x14ac:dyDescent="0.2">
       <c r="M15" s="8" t="s">
         <v>62</v>
       </c>
@@ -6722,17 +6783,17 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:24" x14ac:dyDescent="0.2">
       <c r="M16" s="8" t="s">
         <v>63</v>
       </c>
       <c r="O16" s="9"/>
     </row>
-    <row r="17" spans="11:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="11:15" x14ac:dyDescent="0.2">
       <c r="M17" s="8"/>
       <c r="O17" s="9"/>
     </row>
-    <row r="18" spans="11:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="11:15" x14ac:dyDescent="0.2">
       <c r="K18">
         <v>4</v>
       </c>
@@ -6747,7 +6808,7 @@
       </c>
       <c r="O18" s="9"/>
     </row>
-    <row r="19" spans="11:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="11:15" x14ac:dyDescent="0.2">
       <c r="M19" s="8" t="s">
         <v>65</v>
       </c>
@@ -6755,7 +6816,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="11:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="11:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="M20" s="13" t="s">
         <v>66</v>
       </c>
@@ -6776,21 +6837,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6F871AC-4AC1-4525-A015-906CC042C494}">
   <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="25.1796875" customWidth="1"/>
-    <col min="3" max="3" width="12.08984375" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.1640625" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" customWidth="1"/>
+    <col min="4" max="4" width="11.5" customWidth="1"/>
+    <col min="6" max="6" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J1" s="16" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="C2" s="42" t="s">
         <v>137</v>
       </c>
@@ -6810,7 +6871,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="42" t="s">
@@ -6833,7 +6894,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="38"/>
       <c r="B4" s="39" t="s">
         <v>39</v>
@@ -6854,7 +6915,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="40" t="s">
         <v>130</v>
       </c>
@@ -6881,7 +6942,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="40"/>
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
@@ -6889,7 +6950,7 @@
       <c r="E6" s="16"/>
       <c r="J6" s="16"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="40"/>
       <c r="B7" s="16"/>
       <c r="C7" s="16"/>
@@ -6899,7 +6960,7 @@
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="40">
         <v>1</v>
       </c>
@@ -6921,7 +6982,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="40"/>
       <c r="B9" s="16" t="s">
         <v>245</v>
@@ -6941,7 +7002,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="40"/>
       <c r="B10" s="16" t="s">
         <v>233</v>
@@ -6959,14 +7020,14 @@
         <v>144</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="40"/>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
       <c r="D11" s="41"/>
       <c r="E11" s="16"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="40">
         <v>2</v>
       </c>
@@ -6988,7 +7049,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B13" s="16" t="s">
         <v>247</v>
       </c>
@@ -7007,7 +7068,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="8"/>
       <c r="B14" s="16" t="s">
         <v>234</v>
@@ -7023,11 +7084,11 @@
         <v>144</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="8"/>
       <c r="D15" s="9"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="8">
         <v>3</v>
       </c>
@@ -7048,7 +7109,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="8"/>
       <c r="B17" s="16" t="s">
         <v>249</v>
@@ -7066,7 +7127,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="8"/>
       <c r="B18" s="16" t="s">
         <v>236</v>
@@ -7082,11 +7143,11 @@
         <v>144</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="8"/>
       <c r="D19" s="9"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="8">
         <v>4</v>
       </c>
@@ -7107,7 +7168,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
       <c r="B21" s="16" t="s">
         <v>96</v>
@@ -7125,7 +7186,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="14" t="s">
         <v>238</v>
@@ -7142,7 +7203,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>5</v>
       </c>
@@ -7162,7 +7223,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>242</v>
       </c>
@@ -7179,7 +7240,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
         <v>243</v>
       </c>
@@ -7202,20 +7263,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72E30AB4-1E2F-415D-B46B-0954882CC2D5}">
   <dimension ref="A1:K32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.81640625" customWidth="1"/>
-    <col min="7" max="7" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.26953125" customWidth="1"/>
-    <col min="9" max="9" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.08984375" customWidth="1"/>
+    <col min="2" max="2" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>211</v>
       </c>
@@ -7238,7 +7299,7 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -7259,7 +7320,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -7292,7 +7353,7 @@
       </c>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
@@ -7321,7 +7382,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -7346,7 +7407,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -7363,7 +7424,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="17"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -7379,7 +7440,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -7404,7 +7465,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2</v>
       </c>
@@ -7428,7 +7489,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>3</v>
       </c>
@@ -7453,7 +7514,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>4</v>
       </c>
@@ -7478,7 +7539,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>5</v>
       </c>
@@ -7501,7 +7562,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -7514,7 +7575,7 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -7527,7 +7588,7 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
     </row>
-    <row r="15" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -7540,7 +7601,7 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
-    <row r="16" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -7553,7 +7614,7 @@
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
-    <row r="17" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -7566,7 +7627,7 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
     </row>
-    <row r="18" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -7579,7 +7640,7 @@
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
     </row>
-    <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -7592,7 +7653,7 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -7605,7 +7666,7 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -7618,7 +7679,7 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
     </row>
-    <row r="22" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -7631,7 +7692,7 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
     </row>
-    <row r="23" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -7644,7 +7705,7 @@
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
     </row>
-    <row r="24" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -7657,7 +7718,7 @@
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
     </row>
-    <row r="25" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -7670,7 +7731,7 @@
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
     </row>
-    <row r="26" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -7683,7 +7744,7 @@
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
     </row>
-    <row r="27" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -7696,7 +7757,7 @@
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
     </row>
-    <row r="28" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -7709,7 +7770,7 @@
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
     </row>
-    <row r="29" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -7722,7 +7783,7 @@
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
     </row>
-    <row r="30" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -7735,7 +7796,7 @@
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
     </row>
-    <row r="31" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -7748,7 +7809,7 @@
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
     </row>
-    <row r="32" spans="1:11" ht="17" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -7768,28 +7829,28 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9FDC982-8E68-4C15-ABFD-51EFC138F8DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9FDC982-8E68-4C15-ABFD-51EFC138F8DE}">
   <dimension ref="A1:N24"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.81640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.81640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.7265625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.08984375" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.7265625" style="1"/>
+    <col min="1" max="1" width="8.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.83203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.83203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.1640625" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>129</v>
       </c>
@@ -7806,7 +7867,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -7820,7 +7881,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -7861,7 +7922,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D5" s="1" t="s">
         <v>124</v>
       </c>
@@ -7893,7 +7954,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -7908,7 +7969,7 @@
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="18"/>
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
@@ -7930,7 +7991,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="18"/>
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
@@ -7947,7 +8008,7 @@
       </c>
       <c r="M8" s="18"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="18"/>
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
@@ -7965,7 +8026,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="18"/>
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
@@ -7985,7 +8046,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="18"/>
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
@@ -8005,7 +8066,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="18"/>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -8025,7 +8086,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>10</v>
       </c>
@@ -8060,7 +8121,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="18"/>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
@@ -8077,7 +8138,7 @@
       <c r="L14" s="18"/>
       <c r="M14" s="18"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
@@ -8092,12 +8153,12 @@
       <c r="L15" s="18"/>
       <c r="M15" s="18"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="18">
         <v>1</v>
       </c>
       <c r="B16" s="18"/>
-      <c r="C16" s="56">
+      <c r="C16" s="52">
         <v>1500</v>
       </c>
       <c r="D16" s="18"/>
@@ -8108,14 +8169,14 @@
       <c r="J16" s="18"/>
       <c r="K16" s="18"/>
       <c r="L16" s="18"/>
-      <c r="M16" s="57">
+      <c r="M16" s="53">
         <v>1500</v>
       </c>
       <c r="N16" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="18">
         <v>2</v>
       </c>
@@ -8124,21 +8185,21 @@
       <c r="D17" s="18"/>
       <c r="E17" s="18"/>
       <c r="F17" s="18"/>
-      <c r="G17" s="57">
+      <c r="G17" s="53">
         <v>-14500</v>
       </c>
       <c r="I17" s="18"/>
       <c r="J17" s="18"/>
       <c r="K17" s="18"/>
       <c r="L17" s="18"/>
-      <c r="M17" s="56">
+      <c r="M17" s="52">
         <v>-14500</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="18">
         <v>3</v>
       </c>
@@ -8148,20 +8209,20 @@
       <c r="E18" s="18"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
-      <c r="I18" s="57">
+      <c r="I18" s="53">
         <v>5600</v>
       </c>
       <c r="J18" s="18"/>
       <c r="K18" s="18"/>
       <c r="L18" s="18"/>
-      <c r="M18" s="56">
+      <c r="M18" s="52">
         <v>-5600</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="18">
         <v>4</v>
       </c>
@@ -8172,19 +8233,19 @@
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
       <c r="I19" s="18"/>
-      <c r="J19" s="56">
+      <c r="J19" s="52">
         <v>-990</v>
       </c>
       <c r="K19" s="18"/>
       <c r="L19" s="18"/>
-      <c r="M19" s="57">
+      <c r="M19" s="53">
         <v>990</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="18"/>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
@@ -8201,7 +8262,7 @@
       <c r="L20" s="18"/>
       <c r="M20" s="18"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="18"/>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
@@ -8218,7 +8279,7 @@
       <c r="L21" s="18"/>
       <c r="M21" s="18"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
         <v>10</v>
       </c>
@@ -8273,7 +8334,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="18"/>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
@@ -8288,7 +8349,7 @@
       <c r="L23" s="18"/>
       <c r="M23" s="18"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G24" s="47">
         <f>SUM(B22:G22)</f>
         <v>130600</v>
@@ -8305,183 +8366,182 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42E0D118-6250-462A-BC0B-699E68CA2912}">
   <dimension ref="A12:D39"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.54296875" customWidth="1"/>
-    <col min="5" max="6" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5" customWidth="1"/>
+    <col min="5" max="6" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="19"/>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
       <c r="D12" s="19"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="19"/>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
       <c r="D13" s="19"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="19"/>
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
       <c r="D14" s="19"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="19"/>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
       <c r="D15" s="19"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="19"/>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
       <c r="D16" s="19"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="19"/>
       <c r="B17" s="19"/>
       <c r="C17" s="19"/>
       <c r="D17" s="19"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="19"/>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
       <c r="D18" s="19"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="19"/>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
       <c r="D19" s="19"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="19"/>
       <c r="B20" s="19"/>
       <c r="C20" s="19"/>
       <c r="D20" s="19"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="19"/>
       <c r="B21" s="19"/>
       <c r="C21" s="19"/>
       <c r="D21" s="19"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="19"/>
       <c r="B22" s="19"/>
       <c r="C22" s="19"/>
       <c r="D22" s="19"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="19"/>
       <c r="B23" s="19"/>
       <c r="C23" s="19"/>
       <c r="D23" s="19"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="19"/>
       <c r="B24" s="19"/>
       <c r="C24" s="19"/>
       <c r="D24" s="19"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="19"/>
       <c r="B25" s="19"/>
       <c r="C25" s="19"/>
       <c r="D25" s="19"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="19"/>
       <c r="B26" s="19"/>
       <c r="C26" s="19"/>
       <c r="D26" s="19"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="19"/>
       <c r="B27" s="19"/>
       <c r="C27" s="19"/>
       <c r="D27" s="19"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="19"/>
       <c r="B28" s="19"/>
       <c r="C28" s="19"/>
       <c r="D28" s="19"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="19"/>
       <c r="B29" s="19"/>
       <c r="C29" s="19"/>
       <c r="D29" s="19"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="19"/>
       <c r="B30" s="19"/>
       <c r="C30" s="19"/>
       <c r="D30" s="19"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="19"/>
       <c r="B31" s="19"/>
       <c r="C31" s="19"/>
       <c r="D31" s="19"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="19"/>
       <c r="B32" s="19"/>
       <c r="C32" s="19"/>
       <c r="D32" s="19"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="19"/>
       <c r="B33" s="19"/>
       <c r="C33" s="19"/>
       <c r="D33" s="19"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="19"/>
       <c r="B34" s="19"/>
       <c r="C34" s="19"/>
       <c r="D34" s="19"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="19"/>
       <c r="B35" s="19"/>
       <c r="C35" s="19"/>
       <c r="D35" s="19"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="19"/>
       <c r="B36" s="19"/>
       <c r="C36" s="19"/>
       <c r="D36" s="19"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="19"/>
       <c r="B37" s="19"/>
       <c r="C37" s="19"/>
       <c r="D37" s="19"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="19"/>
       <c r="B38" s="19"/>
       <c r="C38" s="19"/>
       <c r="D38" s="19"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="19"/>
       <c r="B39" s="19"/>
       <c r="C39" s="19"/>
@@ -8496,28 +8556,28 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E3B5B4B-3C34-4932-AF1F-79558FA37AF8}">
   <dimension ref="A1:Q26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.81640625" customWidth="1"/>
-    <col min="3" max="3" width="11.7265625" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="6.08984375" hidden="1" customWidth="1"/>
-    <col min="6" max="7" width="8.81640625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="4.81640625" hidden="1" customWidth="1"/>
-    <col min="9" max="10" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.453125" customWidth="1"/>
-    <col min="12" max="12" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.83203125" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="6.1640625" hidden="1" customWidth="1"/>
+    <col min="6" max="7" width="8.83203125" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="4.83203125" hidden="1" customWidth="1"/>
+    <col min="9" max="10" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.5" customWidth="1"/>
+    <col min="12" max="12" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="8.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>156</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="58" t="s">
+      <c r="C1" s="54" t="s">
         <v>51</v>
       </c>
       <c r="D1" s="21"/>
@@ -8549,7 +8609,7 @@
       <c r="P1" s="21"/>
       <c r="Q1" s="1"/>
     </row>
-    <row r="2" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>220</v>
@@ -8582,7 +8642,7 @@
       </c>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>72</v>
       </c>
@@ -8623,7 +8683,7 @@
       </c>
       <c r="Q3" s="1"/>
     </row>
-    <row r="4" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>75</v>
       </c>
@@ -8653,7 +8713,7 @@
       <c r="P4" s="24"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>76</v>
       </c>
@@ -8683,7 +8743,7 @@
       <c r="P5" s="24"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>96</v>
       </c>
@@ -8717,7 +8777,7 @@
       <c r="P6" s="24"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -8747,7 +8807,7 @@
       <c r="P7" s="24"/>
       <c r="Q7" s="1"/>
     </row>
-    <row r="8" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>146</v>
       </c>
@@ -8781,7 +8841,7 @@
       </c>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>83</v>
       </c>
@@ -8811,7 +8871,7 @@
       </c>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>154</v>
       </c>
@@ -8843,7 +8903,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>155</v>
       </c>
@@ -8871,7 +8931,7 @@
       <c r="P11" s="24"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>147</v>
       </c>
@@ -8901,7 +8961,7 @@
       <c r="P12" s="24"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>148</v>
       </c>
@@ -8935,7 +8995,7 @@
       <c r="P13" s="24"/>
       <c r="Q13" s="1"/>
     </row>
-    <row r="14" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>91</v>
       </c>
@@ -8965,7 +9025,7 @@
       <c r="P14" s="24"/>
       <c r="Q14" s="1"/>
     </row>
-    <row r="15" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>149</v>
       </c>
@@ -8995,7 +9055,7 @@
       <c r="P15" s="24"/>
       <c r="Q15" s="1"/>
     </row>
-    <row r="16" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>150</v>
       </c>
@@ -9019,7 +9079,9 @@
       </c>
       <c r="K16" s="26"/>
       <c r="L16" s="23"/>
-      <c r="M16" s="24"/>
+      <c r="M16" s="24">
+        <v>18</v>
+      </c>
       <c r="N16" s="26"/>
       <c r="O16" s="23"/>
       <c r="P16" s="24">
@@ -9028,7 +9090,7 @@
       </c>
       <c r="Q16" s="1"/>
     </row>
-    <row r="17" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>151</v>
       </c>
@@ -9060,7 +9122,7 @@
       <c r="P17" s="24"/>
       <c r="Q17" s="1"/>
     </row>
-    <row r="18" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>152</v>
       </c>
@@ -9092,7 +9154,7 @@
       <c r="P18" s="24"/>
       <c r="Q18" s="1"/>
     </row>
-    <row r="19" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="23"/>
@@ -9111,7 +9173,7 @@
       <c r="P19" s="24"/>
       <c r="Q19" s="1"/>
     </row>
-    <row r="20" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>153</v>
       </c>
@@ -9134,7 +9196,7 @@
       <c r="P20" s="49"/>
       <c r="Q20" s="50"/>
     </row>
-    <row r="21" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="23"/>
@@ -9153,7 +9215,7 @@
       <c r="P21" s="24"/>
       <c r="Q21" s="1"/>
     </row>
-    <row r="22" spans="1:17" ht="17.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>68</v>
       </c>
@@ -9191,7 +9253,7 @@
       </c>
       <c r="M22" s="28">
         <f t="shared" si="3"/>
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="N22" s="26"/>
       <c r="O22" s="27">
@@ -9204,7 +9266,7 @@
       </c>
       <c r="Q22" s="1"/>
     </row>
-    <row r="23" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -9223,7 +9285,7 @@
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
     </row>
-    <row r="24" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -9242,7 +9304,7 @@
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
     </row>
-    <row r="25" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -9261,7 +9323,7 @@
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
     </row>
-    <row r="26" spans="1:17" ht="17" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -9289,40 +9351,40 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82B5A463-B021-405F-A385-9F30F6BE76DF}">
   <dimension ref="B2:F30"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="24.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.54296875" customWidth="1"/>
-    <col min="4" max="4" width="10.54296875" customWidth="1"/>
-    <col min="5" max="5" width="11.90625" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="3" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="53" t="s">
+    <row r="2" spans="2:5" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="58" t="s">
         <v>159</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-    </row>
-    <row r="4" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="54" t="s">
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+    </row>
+    <row r="4" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="59" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-    </row>
-    <row r="5" spans="2:5" ht="15.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="55" t="s">
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+    </row>
+    <row r="5" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="60" t="s">
         <v>104</v>
       </c>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-    </row>
-    <row r="6" spans="2:5" ht="15" x14ac:dyDescent="0.35">
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+    </row>
+    <row r="6" spans="2:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B6" s="29" t="s">
         <v>17</v>
       </c>
@@ -9334,7 +9396,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="15" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B7" s="29" t="s">
         <v>105</v>
       </c>
@@ -9344,7 +9406,7 @@
       </c>
       <c r="E7" s="34"/>
     </row>
-    <row r="8" spans="2:5" ht="15" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B8" s="29" t="s">
         <v>106</v>
       </c>
@@ -9354,7 +9416,7 @@
       </c>
       <c r="E8" s="34"/>
     </row>
-    <row r="9" spans="2:5" ht="15" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B9" s="29" t="s">
         <v>160</v>
       </c>
@@ -9364,7 +9426,7 @@
       </c>
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="2:5" ht="15" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B10" s="29" t="s">
         <v>107</v>
       </c>
@@ -9374,7 +9436,7 @@
       </c>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="2:5" ht="15" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B11" s="29" t="s">
         <v>161</v>
       </c>
@@ -9384,7 +9446,7 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="2:5" ht="15" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:5" ht="17" x14ac:dyDescent="0.2">
       <c r="B12" s="29" t="s">
         <v>168</v>
       </c>
@@ -9394,7 +9456,7 @@
         <v>46260</v>
       </c>
     </row>
-    <row r="13" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="29" t="s">
         <v>108</v>
       </c>
@@ -9404,7 +9466,7 @@
         <v>15420</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="29" t="s">
         <v>110</v>
       </c>
@@ -9414,7 +9476,7 @@
         <v>5240</v>
       </c>
     </row>
-    <row r="15" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="29" t="s">
         <v>109</v>
       </c>
@@ -9424,7 +9486,7 @@
         <v>8020</v>
       </c>
     </row>
-    <row r="16" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="29" t="s">
         <v>111</v>
       </c>
@@ -9434,7 +9496,7 @@
         <v>20050</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="29" t="s">
         <v>162</v>
       </c>
@@ -9444,7 +9506,7 @@
         <v>17270</v>
       </c>
     </row>
-    <row r="18" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="29" t="s">
         <v>163</v>
       </c>
@@ -9454,7 +9516,7 @@
         <v>46250</v>
       </c>
     </row>
-    <row r="19" spans="2:6" ht="15" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B19" s="29" t="s">
         <v>164</v>
       </c>
@@ -9464,7 +9526,7 @@
       </c>
       <c r="E19" s="35"/>
     </row>
-    <row r="20" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="29" t="s">
         <v>165</v>
       </c>
@@ -9474,7 +9536,7 @@
         <v>180110</v>
       </c>
     </row>
-    <row r="21" spans="2:6" ht="15" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B21" s="29" t="s">
         <v>102</v>
       </c>
@@ -9484,7 +9546,7 @@
       </c>
       <c r="E21" s="35"/>
     </row>
-    <row r="22" spans="2:6" ht="15" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B22" s="29" t="s">
         <v>101</v>
       </c>
@@ -9494,7 +9556,7 @@
       </c>
       <c r="E22" s="35"/>
     </row>
-    <row r="23" spans="2:6" ht="15" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B23" s="29" t="s">
         <v>103</v>
       </c>
@@ -9504,7 +9566,7 @@
       </c>
       <c r="E23" s="35"/>
     </row>
-    <row r="24" spans="2:6" ht="15" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B24" s="29" t="s">
         <v>166</v>
       </c>
@@ -9514,7 +9576,7 @@
       </c>
       <c r="E24" s="35"/>
     </row>
-    <row r="25" spans="2:6" ht="15" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B25" s="29" t="s">
         <v>167</v>
       </c>
@@ -9524,7 +9586,7 @@
       </c>
       <c r="E25" s="35"/>
     </row>
-    <row r="26" spans="2:6" ht="15" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B26" s="29" t="s">
         <v>20</v>
       </c>
@@ -9534,19 +9596,19 @@
       </c>
       <c r="E26" s="35"/>
     </row>
-    <row r="27" spans="2:6" ht="15" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B27" s="29"/>
       <c r="C27" s="29"/>
       <c r="D27" s="33"/>
       <c r="E27" s="35"/>
     </row>
-    <row r="28" spans="2:6" ht="15" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B28" s="29"/>
       <c r="C28" s="29"/>
       <c r="D28" s="33"/>
       <c r="E28" s="35"/>
     </row>
-    <row r="29" spans="2:6" ht="15.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:6" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B29" s="30" t="s">
         <v>68</v>
       </c>
@@ -9561,7 +9623,7 @@
       </c>
       <c r="F29" s="37"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="D30" s="37">
         <f>E29-D29</f>
         <v>0</v>
@@ -9580,18 +9642,18 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D32DA8-B652-4F14-A77B-57571A439ABA}">
   <dimension ref="A1:O34"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.81640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.1796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1796875" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.7265625" style="1"/>
+    <col min="1" max="1" width="33.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.1640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="17.5" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>169</v>
       </c>
@@ -9616,7 +9678,7 @@
       </c>
       <c r="O2" s="21"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C3" s="22" t="s">
         <v>145</v>
       </c>
@@ -9634,7 +9696,7 @@
       <c r="N3" s="22"/>
       <c r="O3" s="3"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>72</v>
       </c>
@@ -9669,7 +9731,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>75</v>
       </c>
@@ -9687,7 +9749,7 @@
       <c r="N5" s="22"/>
       <c r="O5" s="3"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>76</v>
       </c>
@@ -9705,7 +9767,7 @@
       <c r="N6" s="22"/>
       <c r="O6" s="3"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>77</v>
       </c>
@@ -9723,7 +9785,7 @@
       <c r="N7" s="22"/>
       <c r="O7" s="3"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>78</v>
       </c>
@@ -9741,7 +9803,7 @@
       <c r="N8" s="22"/>
       <c r="O8" s="3"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>79</v>
       </c>
@@ -9759,7 +9821,7 @@
       <c r="N9" s="22"/>
       <c r="O9" s="3"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>80</v>
       </c>
@@ -9777,7 +9839,7 @@
       <c r="N10" s="22"/>
       <c r="O10" s="3"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>81</v>
       </c>
@@ -9795,7 +9857,7 @@
       <c r="N11" s="22"/>
       <c r="O11" s="3"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>82</v>
       </c>
@@ -9813,7 +9875,7 @@
       <c r="N12" s="22"/>
       <c r="O12" s="3"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>83</v>
       </c>
@@ -9831,7 +9893,7 @@
       <c r="N13" s="22"/>
       <c r="O13" s="3"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>84</v>
       </c>
@@ -9849,7 +9911,7 @@
       <c r="N14" s="22"/>
       <c r="O14" s="3"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>85</v>
       </c>
@@ -9867,7 +9929,7 @@
       <c r="N15" s="22"/>
       <c r="O15" s="3"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>86</v>
       </c>
@@ -9885,7 +9947,7 @@
       <c r="N16" s="22"/>
       <c r="O16" s="3"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>87</v>
       </c>
@@ -9903,7 +9965,7 @@
       <c r="N17" s="22"/>
       <c r="O17" s="3"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>88</v>
       </c>
@@ -9921,7 +9983,7 @@
       <c r="N18" s="22"/>
       <c r="O18" s="3"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>89</v>
       </c>
@@ -9939,7 +10001,7 @@
       <c r="N19" s="22"/>
       <c r="O19" s="3"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>90</v>
       </c>
@@ -9957,7 +10019,7 @@
       <c r="N20" s="22"/>
       <c r="O20" s="3"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>91</v>
       </c>
@@ -9975,7 +10037,7 @@
       <c r="N21" s="22"/>
       <c r="O21" s="3"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>92</v>
       </c>
@@ -9993,7 +10055,7 @@
       <c r="N22" s="22"/>
       <c r="O22" s="3"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>172</v>
       </c>
@@ -10011,7 +10073,7 @@
       <c r="N23" s="22"/>
       <c r="O23" s="3"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>93</v>
       </c>
@@ -10027,7 +10089,7 @@
       <c r="N24" s="22"/>
       <c r="O24" s="3"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>94</v>
       </c>
@@ -10043,7 +10105,7 @@
       <c r="N25" s="22"/>
       <c r="O25" s="3"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>95</v>
       </c>
@@ -10059,7 +10121,7 @@
       <c r="N26" s="22"/>
       <c r="O26" s="3"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>96</v>
       </c>
@@ -10075,7 +10137,7 @@
       <c r="N27" s="22"/>
       <c r="O27" s="3"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>97</v>
       </c>
@@ -10091,7 +10153,7 @@
       <c r="N28" s="22"/>
       <c r="O28" s="3"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>98</v>
       </c>
@@ -10107,7 +10169,7 @@
       <c r="N29" s="22"/>
       <c r="O29" s="3"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>99</v>
       </c>
@@ -10123,7 +10185,7 @@
       <c r="N30" s="22"/>
       <c r="O30" s="3"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C31" s="23"/>
       <c r="D31" s="24"/>
       <c r="E31" s="26"/>
@@ -10136,7 +10198,7 @@
       <c r="N31" s="22"/>
       <c r="O31" s="3"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>100</v>
       </c>
@@ -10152,7 +10214,7 @@
       <c r="N32" s="22"/>
       <c r="O32" s="3"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C33" s="23"/>
       <c r="D33" s="24"/>
       <c r="E33" s="26"/>
@@ -10165,7 +10227,7 @@
       <c r="N33" s="22"/>
       <c r="O33" s="3"/>
     </row>
-    <row r="34" spans="1:15" ht="17.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>68</v>
       </c>
